--- a/artfynd/A 16043-2025 artfynd.xlsx
+++ b/artfynd/A 16043-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>122518752</v>
       </c>
       <c r="B3" t="n">
-        <v>57437</v>
+        <v>57440</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 16043-2025 artfynd.xlsx
+++ b/artfynd/A 16043-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>122518752</v>
       </c>
       <c r="B3" t="n">
-        <v>57440</v>
+        <v>57441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 16043-2025 artfynd.xlsx
+++ b/artfynd/A 16043-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>96115449</v>
       </c>
       <c r="B2" t="n">
-        <v>56437</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604651.0884552271</v>
+        <v>604651</v>
       </c>
       <c r="R2" t="n">
-        <v>6942975.2926869</v>
+        <v>6942975</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -760,19 +755,9 @@
           <t>2021-09-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,32 +784,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122518752</v>
+        <v>111143012</v>
       </c>
       <c r="B3" t="n">
-        <v>57441</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102621</v>
+        <v>100100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -881,22 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,6 +890,244 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122518752</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hallsta, Tomming, Indal, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>604651</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6942975</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Michael Englevid</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Michael Englevid</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>98625056</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57785</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hallsta, Tomming, Indal, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>604651</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6942975</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-02-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-02-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Michael Englevid</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Michael Englevid</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16043-2025 artfynd.xlsx
+++ b/artfynd/A 16043-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,27 +784,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111143012</v>
+        <v>135190706</v>
       </c>
       <c r="B3" t="n">
-        <v>57838</v>
+        <v>57921</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100100</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122518752</v>
+        <v>111143012</v>
       </c>
       <c r="B4" t="n">
-        <v>57794</v>
+        <v>57838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102621</v>
+        <v>100100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -970,22 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,27 +1002,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98625056</v>
+        <v>122518752</v>
       </c>
       <c r="B5" t="n">
-        <v>57785</v>
+        <v>57794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102622</v>
+        <v>102621</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1049,7 +1039,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1089,22 +1079,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-02-14</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-02-14</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,6 +1118,125 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>98625056</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57785</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hallsta, Tomming, Indal, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>604651</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6942975</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-02-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-02-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Englevid</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Englevid</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16043-2025 artfynd.xlsx
+++ b/artfynd/A 16043-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96115449</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135190706</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111143012</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122518752</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,8 +1262,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98625056</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 16043-2025 artfynd.xlsx
+++ b/artfynd/A 16043-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>135190706</v>
       </c>
       <c r="B3" t="n">
-        <v>57921</v>
+        <v>57926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16043-2025 artfynd.xlsx
+++ b/artfynd/A 16043-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,27 +794,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111143012</v>
+        <v>135190706</v>
       </c>
       <c r="B3" t="n">
-        <v>57838</v>
+        <v>57926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100100</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,16 +902,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111143012</t>
+          <t>https://artportalen.se/Sighting/135190706</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122518752</v>
+        <v>111143012</v>
       </c>
       <c r="B4" t="n">
-        <v>57794</v>
+        <v>57838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,16 +919,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102621</v>
+        <v>100100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -985,22 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,33 +1016,33 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122518752</t>
+          <t>https://artportalen.se/Sighting/111143012</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98625056</v>
+        <v>122518752</v>
       </c>
       <c r="B5" t="n">
-        <v>57785</v>
+        <v>57794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102622</v>
+        <v>102621</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1069,7 +1059,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1109,22 +1099,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-02-14</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-02-14</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,6 +1139,130 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122518752</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>98625056</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57785</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hallsta, Tomming, Indal, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>604651</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6942975</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-02-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-02-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Englevid</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Englevid</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/98625056</t>
         </is>
@@ -1160,6 +1274,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
